--- a/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>158 MI SEGUNDA CASITA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-3.7901</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-73.29349999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>333</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-3.7901</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-73.2935</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>168 GOTITAS DEL SABER</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-3.78597</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-73.33972799999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>249</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-3.78597</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-73.339728</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>317</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-3.7739</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-73.27485</v>
-      </c>
-      <c r="I4" t="n">
-        <v>445</v>
-      </c>
-      <c r="J4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-3.7739</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-73.27485</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>318 GLORIA CHAVEZ CULQUI</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-3.77391</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-73.29031000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>460</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-3.77391</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-73.29031</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>348 DELIA PEREA TORRES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-3.823355</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-73.327972</v>
-      </c>
-      <c r="I6" t="n">
-        <v>277</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-3.823355</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-73.327972</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>364</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-3.76677</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-73.27930000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>266</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-3.76677</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-73.2793</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>396 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-3.766563</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-73.278856</v>
-      </c>
-      <c r="I8" t="n">
-        <v>310</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-3.766563</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-73.278856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>474 ANGELITOS DEL SABER</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-3.77282</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-73.28157</v>
-      </c>
-      <c r="I9" t="n">
-        <v>139</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-3.77282</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-73.28157</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>530</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-3.843849</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-73.33998</v>
-      </c>
-      <c r="I10" t="n">
-        <v>202</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-3.843849</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-73.33998</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>548 MI MUNDO INFANTIL</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-3.7792</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-73.2912</v>
-      </c>
-      <c r="I11" t="n">
-        <v>511</v>
-      </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-3.7792</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-73.2912</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>591</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-3.78219</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-73.28514</v>
-      </c>
-      <c r="I12" t="n">
-        <v>301</v>
-      </c>
-      <c r="J12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-3.78219</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-73.28514</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>APLICACION UNAP</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-3.7815</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-73.28538</v>
-      </c>
-      <c r="I13" t="n">
-        <v>898</v>
-      </c>
-      <c r="J13" t="n">
-        <v>38</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-3.7815</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-73.28538</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>690 SANTA MONICA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-3.76748</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.27315</v>
-      </c>
-      <c r="I14" t="n">
-        <v>203</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-3.76748</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-73.27315</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>692</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-3.78891</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-73.29935</v>
-      </c>
-      <c r="I15" t="n">
-        <v>208</v>
-      </c>
-      <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-3.78891</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-73.29935</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>60024 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-3.77449</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.29006</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2931</v>
-      </c>
-      <c r="J16" t="n">
-        <v>109</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-3.77449</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.29006</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2931</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>60027</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-3.786487</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-73.33911500000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J17" t="n">
-        <v>52</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.786487</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-73.339115</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>60093 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-3.80519</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-73.340785</v>
-      </c>
-      <c r="I18" t="n">
-        <v>917</v>
-      </c>
-      <c r="J18" t="n">
-        <v>48</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.80519</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-73.340785</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>60094</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-3.828828</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-73.355177</v>
-      </c>
-      <c r="I19" t="n">
-        <v>373</v>
-      </c>
-      <c r="J19" t="n">
-        <v>19</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-3.828828</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.355177</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>60102</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-3.889641</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-73.35390599999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>513</v>
-      </c>
-      <c r="J20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-3.889641</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-73.353906</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>60110</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-3.823057</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-73.32639399999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1552</v>
-      </c>
-      <c r="J21" t="n">
-        <v>62</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-3.823057</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-73.326394</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>60113</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-3.780437</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-73.312084</v>
-      </c>
-      <c r="I22" t="n">
-        <v>667</v>
-      </c>
-      <c r="J22" t="n">
-        <v>29</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-3.780437</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-73.312084</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>60128 MARIA ANTONIETA RODRIGUEZ MACEDA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-3.863287</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-73.336562</v>
-      </c>
-      <c r="I23" t="n">
-        <v>436</v>
-      </c>
-      <c r="J23" t="n">
-        <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-3.863287</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-73.336562</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>60133</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-4.231024</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-73.48778</v>
-      </c>
-      <c r="I24" t="n">
-        <v>423</v>
-      </c>
-      <c r="J24" t="n">
-        <v>18</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-4.231024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-73.48778</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>60778</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-3.844742</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-73.386899</v>
-      </c>
-      <c r="I25" t="n">
-        <v>296</v>
-      </c>
-      <c r="J25" t="n">
-        <v>24</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-3.844742</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-73.386899</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>601324 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-3.7733</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-73.28112</v>
-      </c>
-      <c r="I26" t="n">
-        <v>605</v>
-      </c>
-      <c r="J26" t="n">
-        <v>26</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-3.7733</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-73.28112</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>601325 CARMEN ROSA PANDURO RAMIREZ</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-3.76663</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-73.28214</v>
-      </c>
-      <c r="I27" t="n">
-        <v>382</v>
-      </c>
-      <c r="J27" t="n">
-        <v>17</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-3.76663</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-73.28214</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>601331</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-4.021036</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-73.432948</v>
-      </c>
-      <c r="I28" t="n">
-        <v>257</v>
-      </c>
-      <c r="J28" t="n">
-        <v>21</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-4.021036</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-73.432948</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>601332</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-3.77915</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-73.28175</v>
-      </c>
-      <c r="I29" t="n">
-        <v>514</v>
-      </c>
-      <c r="J29" t="n">
-        <v>23</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-3.77915</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-73.28175</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>601387</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-3.77069</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-73.27883</v>
-      </c>
-      <c r="I30" t="n">
-        <v>324</v>
-      </c>
-      <c r="J30" t="n">
-        <v>20</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-3.77069</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-73.27883</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>601409</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-3.79036</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-73.30287</v>
-      </c>
-      <c r="I31" t="n">
-        <v>461</v>
-      </c>
-      <c r="J31" t="n">
-        <v>24</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-3.79036</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-73.30287</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>601411 MELVIN JONES</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-3.761201</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-73.272904</v>
-      </c>
-      <c r="I32" t="n">
-        <v>840</v>
-      </c>
-      <c r="J32" t="n">
-        <v>32</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-3.761201</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-73.272904</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>601453</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-4.22045</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-73.48138</v>
-      </c>
-      <c r="I33" t="n">
-        <v>216</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-4.22045</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-73.48138</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>601497</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-3.7853</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-73.2869</v>
-      </c>
-      <c r="I34" t="n">
-        <v>972</v>
-      </c>
-      <c r="J34" t="n">
-        <v>44</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-3.7853</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-73.2869</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>601515</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-3.79122</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-73.29419</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1479</v>
-      </c>
-      <c r="J35" t="n">
-        <v>64</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-3.79122</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-73.29419</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>601540 MONS. GABINO PERAL DE LA TORRE</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-3.809807</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-73.316677</v>
-      </c>
-      <c r="I36" t="n">
-        <v>265</v>
-      </c>
-      <c r="J36" t="n">
-        <v>12</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-3.809807</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-73.316677</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>6010194 MARIA SOCORRO MENDOZA MENDOZA / 794</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-3.783177</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-73.29915099999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>870</v>
-      </c>
-      <c r="J37" t="n">
-        <v>35</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-3.783177</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-73.299151</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>6010227 CLUB DE LEONES DE LEMGO ALEMANIA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-3.78157</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-73.28209</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1510</v>
-      </c>
-      <c r="J38" t="n">
-        <v>62</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-3.78157</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-73.28209</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>6010231</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-4.091835</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-73.45320100000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>379</v>
-      </c>
-      <c r="J39" t="n">
-        <v>22</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-4.091835</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-73.453201</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>6010274</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-3.84262</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-73.336792</v>
-      </c>
-      <c r="I40" t="n">
-        <v>504</v>
-      </c>
-      <c r="J40" t="n">
-        <v>23</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-3.84262</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-73.336792</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>6010275 FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-3.78161</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-73.29532</v>
-      </c>
-      <c r="I41" t="n">
-        <v>784</v>
-      </c>
-      <c r="J41" t="n">
-        <v>36</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-3.78161</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-73.29532</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>EL MILAGRO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-3.93753</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-73.37275</v>
-      </c>
-      <c r="I42" t="n">
-        <v>252</v>
-      </c>
-      <c r="J42" t="n">
-        <v>12</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-3.93753</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-73.37275</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>COLEGIO NACIONAL IQUITOS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-3.7654</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-73.26864</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2432</v>
-      </c>
-      <c r="J43" t="n">
-        <v>144</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-3.7654</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-73.26864</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>762</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-3.7851</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-73.2871</v>
-      </c>
-      <c r="I44" t="n">
-        <v>249</v>
-      </c>
-      <c r="J44" t="n">
-        <v>11</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-3.7851</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-73.2871</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>763</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-3.799061</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-73.30989599999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>282</v>
-      </c>
-      <c r="J45" t="n">
-        <v>11</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-3.799061</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-73.309896</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>601491 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-3.79099</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-73.30119999999999</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2305</v>
-      </c>
-      <c r="J46" t="n">
-        <v>81</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-3.79099</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-73.3012</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>FE Y ALEGRIA 46 WILHEM ROSSMAN</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-3.77839</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-73.29181</v>
-      </c>
-      <c r="I47" t="n">
-        <v>896</v>
-      </c>
-      <c r="J47" t="n">
-        <v>37</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-3.77839</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-73.29181</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>UNAP MARIA REICHE</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-3.766469</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-73.273014</v>
-      </c>
-      <c r="I48" t="n">
-        <v>139</v>
-      </c>
-      <c r="J48" t="n">
-        <v>6</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-3.766469</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-73.273014</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>INKA MANKO KALI</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-3.794203</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-73.298965</v>
-      </c>
-      <c r="I49" t="n">
-        <v>373</v>
-      </c>
-      <c r="J49" t="n">
-        <v>16</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-3.794203</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-73.298965</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>601693</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-3.795034</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-73.336111</v>
-      </c>
-      <c r="I50" t="n">
-        <v>409</v>
-      </c>
-      <c r="J50" t="n">
-        <v>17</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-3.795034</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-73.336111</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>895</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-3.795034</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-73.336111</v>
-      </c>
-      <c r="I51" t="n">
-        <v>200</v>
-      </c>
-      <c r="J51" t="n">
-        <v>9</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-3.795034</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-73.336111</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>FUENTE DE SABER / FUENTE DEL SABER</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-3.76822</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-73.27495999999999</v>
-      </c>
-      <c r="I52" t="n">
-        <v>226</v>
-      </c>
-      <c r="J52" t="n">
-        <v>24</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-3.76822</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-73.27496</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>601581 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-3.798577</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-73.307457</v>
-      </c>
-      <c r="I53" t="n">
-        <v>583</v>
-      </c>
-      <c r="J53" t="n">
-        <v>23</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-3.798577</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-73.307457</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>601608</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-3.84446</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-73.339311</v>
-      </c>
-      <c r="I54" t="n">
-        <v>987</v>
-      </c>
-      <c r="J54" t="n">
-        <v>29</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-3.84446</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-73.339311</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>601606 VIOLETA CORREA DE BELAUNDE</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-3.781896</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-73.273662</v>
-      </c>
-      <c r="I55" t="n">
-        <v>866</v>
-      </c>
-      <c r="J55" t="n">
-        <v>33</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-3.781896</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-73.273662</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>601083 REINO UNIDO</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-3.79692</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-73.313503</v>
-      </c>
-      <c r="I56" t="n">
-        <v>305</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-3.79692</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-73.313503</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>601747</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-3.874315</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-73.35857799999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>358</v>
-      </c>
-      <c r="J57" t="n">
-        <v>26</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-3.874315</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-73.358578</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>601412</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-3.85465</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-73.34966</v>
-      </c>
-      <c r="I58" t="n">
-        <v>220</v>
-      </c>
-      <c r="J58" t="n">
-        <v>15</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-3.85465</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-73.34966</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>CRISTO REDENTOR</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-3.780654</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-73.292124</v>
-      </c>
-      <c r="I59" t="n">
-        <v>487</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-3.780654</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-73.292124</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>364043</t>
+          <t>364076</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>158 MI SEGUNDA CASITA</t>
+          <t>168 GOTITAS DEL SABER</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.7901</t>
+          <t>-3.78597</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.2935</t>
+          <t>-73.339728</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>364076</t>
+          <t>365194</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>168 GOTITAS DEL SABER</t>
+          <t>60024 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.78597</t>
+          <t>-3.77449</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.339728</t>
+          <t>-73.29006</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>364203</t>
+          <t>367131</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>762</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.7739</t>
+          <t>-3.7851</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.27485</t>
+          <t>-73.2871</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>364217</t>
+          <t>367145</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>318 GLORIA CHAVEZ CULQUI</t>
+          <t>763</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.77391</t>
+          <t>-3.799061</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.29031</t>
+          <t>-73.309896</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>364364</t>
+          <t>366631</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>396 JUAN PABLO II</t>
+          <t>601540 MONS. GABINO PERAL DE LA TORRE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.766563</t>
+          <t>-3.809807</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.278856</t>
+          <t>-73.316677</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>364458</t>
+          <t>366909</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>474 ANGELITOS DEL SABER</t>
+          <t>EL MILAGRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.77282</t>
+          <t>-3.93753</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.28157</t>
+          <t>-73.37275</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>364552</t>
+          <t>364364</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>396 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.843849</t>
+          <t>-3.766563</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.33998</t>
+          <t>-73.278856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>364670</t>
+          <t>364726</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>548 MI MUNDO INFANTIL</t>
+          <t>591</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.7792</t>
+          <t>-3.78219</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.2912</t>
+          <t>-73.28514</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>364726</t>
+          <t>364043</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>158 MI SEGUNDA CASITA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.78219</t>
+          <t>-3.7901</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.28514</t>
+          <t>-73.2935</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>364849</t>
+          <t>366476</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>APLICACION UNAP</t>
+          <t>601453</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.7815</t>
+          <t>-4.22045</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.28538</t>
+          <t>-73.48138</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>364887</t>
+          <t>367065</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>690 SANTA MONICA</t>
+          <t>COLEGIO NACIONAL IQUITOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.76748</t>
+          <t>-3.7654</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.27315</t>
+          <t>-73.26864</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>364905</t>
+          <t>823955</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>601412</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.78891</t>
+          <t>-3.85465</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.29935</t>
+          <t>-73.34966</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,42 +1369,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>365194</t>
+          <t>368036</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60024 SAN JUAN DE MIRAFLORES</t>
+          <t>INKA MANKO KALI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.77449</t>
+          <t>-3.794203</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.29006</t>
+          <t>-73.298965</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>365226</t>
+          <t>364217</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>318 GLORIA CHAVEZ CULQUI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.786487</t>
+          <t>-3.77391</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.339115</t>
+          <t>-73.29031</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>365368</t>
+          <t>366216</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60093 JOSE OLAYA BALANDRA</t>
+          <t>601325 CARMEN ROSA PANDURO RAMIREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.80519</t>
+          <t>-3.76663</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.340785</t>
+          <t>-73.28214</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>382</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>365373</t>
+          <t>559564</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>601693</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.828828</t>
+          <t>-3.795034</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.355177</t>
+          <t>-73.336111</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>365434</t>
+          <t>365622</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60102</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.889641</t>
+          <t>-4.231024</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.353906</t>
+          <t>-73.48778</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>423</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>365491</t>
+          <t>364203</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>317</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.823057</t>
+          <t>-3.7739</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-73.326394</t>
+          <t>-73.27485</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>445</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>365518</t>
+          <t>365373</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60113</t>
+          <t>60094</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.780437</t>
+          <t>-3.828828</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-73.312084</t>
+          <t>-73.355177</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>365599</t>
+          <t>741889</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60128 MARIA ANTONIETA RODRIGUEZ MACEDA</t>
+          <t>601083 REINO UNIDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.863287</t>
+          <t>-3.79692</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-73.336562</t>
+          <t>-73.313503</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>365622</t>
+          <t>366315</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60133</t>
+          <t>601387</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.231024</t>
+          <t>-3.77069</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-73.48778</t>
+          <t>-73.27883</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>365797</t>
+          <t>366259</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>601331</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.844742</t>
+          <t>-4.021036</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-73.386899</t>
+          <t>-73.432948</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>366202</t>
+          <t>831743</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>601324 VIRGEN DE LAS MERCEDES</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.7733</t>
+          <t>-3.780654</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-73.28112</t>
+          <t>-73.292124</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>366216</t>
+          <t>366787</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>601325 CARMEN ROSA PANDURO RAMIREZ</t>
+          <t>6010231</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.76663</t>
+          <t>-4.091835</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-73.28214</t>
+          <t>-73.453201</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>366259</t>
+          <t>366264</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>601331</t>
+          <t>601332</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.021036</t>
+          <t>-3.77915</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-73.432948</t>
+          <t>-73.28175</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>514</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,27 +2175,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>366264</t>
+          <t>366805</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>601332</t>
+          <t>6010274</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.77915</t>
+          <t>-3.84262</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-73.28175</t>
+          <t>-73.336792</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>366315</t>
+          <t>740352</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>601387</t>
+          <t>601581 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.77069</t>
+          <t>-3.798577</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-73.27883</t>
+          <t>-73.307457</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>583</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,27 +2299,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>366344</t>
+          <t>364670</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>601409</t>
+          <t>548 MI MUNDO INFANTIL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.79036</t>
+          <t>-3.7792</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-73.30287</t>
+          <t>-73.2912</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>366363</t>
+          <t>365797</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>601411 MELVIN JONES</t>
+          <t>60778</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.761201</t>
+          <t>-3.844742</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-73.272904</t>
+          <t>-73.386899</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>366476</t>
+          <t>366344</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>601453</t>
+          <t>601409</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.22045</t>
+          <t>-3.79036</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-73.48138</t>
+          <t>-73.30287</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>366513</t>
+          <t>651138</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>601497</t>
+          <t>FUENTE DE SABER / FUENTE DEL SABER</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.7853</t>
+          <t>-3.76822</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-73.2869</t>
+          <t>-73.27496</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>366589</t>
+          <t>365434</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>601515</t>
+          <t>60102</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.79122</t>
+          <t>-3.889641</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-73.29419</t>
+          <t>-73.353906</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>513</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>366631</t>
+          <t>365599</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>601540 MONS. GABINO PERAL DE LA TORRE</t>
+          <t>60128 MARIA ANTONIETA RODRIGUEZ MACEDA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.809807</t>
+          <t>-3.863287</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-73.316677</t>
+          <t>-73.336562</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>366730</t>
+          <t>366202</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6010194 MARIA SOCORRO MENDOZA MENDOZA / 794</t>
+          <t>601324 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.783177</t>
+          <t>-3.7733</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-73.299151</t>
+          <t>-73.28112</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>605</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>366768</t>
+          <t>815559</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6010227 CLUB DE LEONES DE LEMGO ALEMANIA</t>
+          <t>601747</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.78157</t>
+          <t>-3.874315</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-73.28209</t>
+          <t>-73.358578</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>358</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>366787</t>
+          <t>365518</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6010231</t>
+          <t>60113</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.091835</t>
+          <t>-3.780437</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-73.453201</t>
+          <t>-73.312084</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>366805</t>
+          <t>740795</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>6010274</t>
+          <t>601608</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.84262</t>
+          <t>-3.84446</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-73.336792</t>
+          <t>-73.339311</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>987</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>366810</t>
+          <t>366363</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6010275 FRANCISCO SECADA VIGNETTA</t>
+          <t>601411 MELVIN JONES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.78161</t>
+          <t>-3.761201</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-73.29532</t>
+          <t>-73.272904</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>840</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>366909</t>
+          <t>740936</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EL MILAGRO</t>
+          <t>601606 VIOLETA CORREA DE BELAUNDE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.93753</t>
+          <t>-3.781896</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-73.37275</t>
+          <t>-73.273662</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>866</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>367065</t>
+          <t>366730</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>COLEGIO NACIONAL IQUITOS</t>
+          <t>6010194 MARIA SOCORRO MENDOZA MENDOZA / 794</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.7654</t>
+          <t>-3.783177</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-73.26864</t>
+          <t>-73.299151</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>367131</t>
+          <t>366810</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>6010275 FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.7851</t>
+          <t>-3.78161</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-73.2871</t>
+          <t>-73.29532</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>784</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>367145</t>
+          <t>367466</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>FE Y ALEGRIA 46 WILHEM ROSSMAN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.799061</t>
+          <t>-3.77839</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-73.309896</t>
+          <t>-73.29181</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>896</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>367193</t>
+          <t>364849</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>601491 MADRE TERESA DE CALCUTA</t>
+          <t>APLICACION UNAP</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.79099</t>
+          <t>-3.7815</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-73.3012</t>
+          <t>-73.28538</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>898</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>367466</t>
+          <t>366513</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 46 WILHEM ROSSMAN</t>
+          <t>601497</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.77839</t>
+          <t>-3.7853</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-73.29181</t>
+          <t>-73.2869</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>972</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>367961</t>
+          <t>365368</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNAP MARIA REICHE</t>
+          <t>60093 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.766469</t>
+          <t>-3.80519</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-73.273014</t>
+          <t>-73.340785</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>917</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>368036</t>
+          <t>365226</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>INKA MANKO KALI</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.794203</t>
+          <t>-3.786487</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-73.298965</t>
+          <t>-73.339115</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>559564</t>
+          <t>364458</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>601693</t>
+          <t>474 ANGELITOS DEL SABER</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.795034</t>
+          <t>-3.77282</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-73.336111</t>
+          <t>-73.28157</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>139</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>559578</t>
+          <t>367961</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>UNAP MARIA REICHE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.795034</t>
+          <t>-3.766469</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-73.336111</t>
+          <t>-73.273014</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>139</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>651138</t>
+          <t>365491</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FUENTE DE SABER / FUENTE DEL SABER</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-3.76822</t>
+          <t>-3.823057</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-73.27496</t>
+          <t>-73.326394</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>740352</t>
+          <t>366768</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>601581 CORAZON DE JESUS</t>
+          <t>6010227 CLUB DE LEONES DE LEMGO ALEMANIA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-3.798577</t>
+          <t>-3.78157</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-73.307457</t>
+          <t>-73.28209</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>740795</t>
+          <t>366589</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>601608</t>
+          <t>601515</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-3.84446</t>
+          <t>-3.79122</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-73.339311</t>
+          <t>-73.29419</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>740936</t>
+          <t>367193</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>601606 VIOLETA CORREA DE BELAUNDE</t>
+          <t>601491 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-3.781896</t>
+          <t>-3.79099</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-73.273662</t>
+          <t>-73.3012</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>741889</t>
+          <t>364552</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>601083 REINO UNIDO</t>
+          <t>530</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-3.79692</t>
+          <t>-3.843849</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-73.313503</t>
+          <t>-73.33998</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>815559</t>
+          <t>364887</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>601747</t>
+          <t>690 SANTA MONICA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-3.874315</t>
+          <t>-3.76748</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-73.358578</t>
+          <t>-73.27315</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>823955</t>
+          <t>364905</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>601412</t>
+          <t>692</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3.85465</t>
+          <t>-3.78891</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-73.34966</t>
+          <t>-73.29935</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>831743</t>
+          <t>559578</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>895</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.780654</t>
+          <t>-3.795034</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-73.292124</t>
+          <t>-73.336111</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>364076</t>
+          <t>831743</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>168 GOTITAS DEL SABER</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.78597</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-73.339728</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-3.780654</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-73.292124</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>365194</t>
+          <t>823955</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60024 SAN JUAN DE MIRAFLORES</t>
+          <t>601412</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.77449</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-73.29006</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>-3.85465</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>-73.34966</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>367131</t>
+          <t>815559</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>601747</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.7851</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-73.2871</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-3.874315</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.358578</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>367145</t>
+          <t>741889</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>601083 REINO UNIDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.799061</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-73.309896</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-3.79692</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-73.313503</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>364302</t>
+          <t>740936</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>348 DELIA PEREA TORRES</t>
+          <t>601606 VIOLETA CORREA DE BELAUNDE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.823355</t>
+          <t>866</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.327972</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-3.781896</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-73.273662</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>364321</t>
+          <t>740795</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>601608</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.76677</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-73.2793</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-3.84446</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-73.339311</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>366631</t>
+          <t>740352</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>601540 MONS. GABINO PERAL DE LA TORRE</t>
+          <t>601581 CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.809807</t>
+          <t>583</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-73.316677</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-3.798577</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-73.307457</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>366909</t>
+          <t>651138</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EL MILAGRO</t>
+          <t>FUENTE DE SABER / FUENTE DEL SABER</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.93753</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-73.37275</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-3.76822</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-73.27496</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>364364</t>
+          <t>559578</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>396 JUAN PABLO II</t>
+          <t>895</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.766563</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-73.278856</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-3.795034</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-73.336111</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>364726</t>
+          <t>559564</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>601693</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.78219</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-73.28514</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-3.795034</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-73.336111</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>364043</t>
+          <t>368036</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158 MI SEGUNDA CASITA</t>
+          <t>INKA MANKO KALI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.7901</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-73.2935</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-3.794203</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-73.298965</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>366476</t>
+          <t>367961</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>601453</t>
+          <t>UNAP MARIA REICHE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.22045</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-73.48138</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-3.766469</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-73.273014</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>367065</t>
+          <t>367466</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COLEGIO NACIONAL IQUITOS</t>
+          <t>FE Y ALEGRIA 46 WILHEM ROSSMAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.7654</t>
+          <t>896</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-73.26864</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>-3.77839</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>-73.29181</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>823955</t>
+          <t>367193</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>601412</t>
+          <t>601491 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.85465</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-73.34966</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-3.79099</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-73.3012</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>368036</t>
+          <t>367145</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INKA MANKO KALI</t>
+          <t>763</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.794203</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.298965</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-3.799061</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-73.309896</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>364217</t>
+          <t>367131</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>318 GLORIA CHAVEZ CULQUI</t>
+          <t>762</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.77391</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.29031</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-3.7851</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.2871</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>366216</t>
+          <t>367065</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>601325 CARMEN ROSA PANDURO RAMIREZ</t>
+          <t>COLEGIO NACIONAL IQUITOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.76663</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-73.28214</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>-3.7654</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.26864</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>559564</t>
+          <t>366909</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>601693</t>
+          <t>EL MILAGRO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.795034</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.336111</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>-3.93753</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-73.37275</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>365622</t>
+          <t>366810</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60133</t>
+          <t>6010275 FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.231024</t>
+          <t>784</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-73.48778</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>-3.78161</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-73.29532</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>364203</t>
+          <t>366805</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>6010274</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.7739</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-73.27485</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>-3.84262</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-73.336792</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>365373</t>
+          <t>366787</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>6010231</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.828828</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-73.355177</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-4.091835</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-73.453201</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>741889</t>
+          <t>366768</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>601083 REINO UNIDO</t>
+          <t>6010227 CLUB DE LEONES DE LEMGO ALEMANIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.79692</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-73.313503</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-3.78157</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-73.28209</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>366315</t>
+          <t>366730</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>601387</t>
+          <t>6010194 MARIA SOCORRO MENDOZA MENDOZA / 794</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.77069</t>
+          <t>870</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-73.27883</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-3.783177</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-73.299151</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>366259</t>
+          <t>366631</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>601331</t>
+          <t>601540 MONS. GABINO PERAL DE LA TORRE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.021036</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-73.432948</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-3.809807</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-73.316677</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>831743</t>
+          <t>366589</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>601515</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.780654</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-73.292124</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-3.79122</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-73.29419</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>366787</t>
+          <t>366513</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6010231</t>
+          <t>601497</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.091835</t>
+          <t>972</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-73.453201</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-3.7853</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-73.2869</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>366264</t>
+          <t>366476</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>601332</t>
+          <t>601453</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.77915</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-73.28175</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>-4.22045</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-73.48138</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>366805</t>
+          <t>366363</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6010274</t>
+          <t>601411 MELVIN JONES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.84262</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-73.336792</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-3.761201</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-73.272904</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>740352</t>
+          <t>366344</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>601581 CORAZON DE JESUS</t>
+          <t>601409</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.798577</t>
+          <t>461</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-73.307457</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>-3.79036</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-73.30287</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>364670</t>
+          <t>366315</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>548 MI MUNDO INFANTIL</t>
+          <t>601387</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-3.7792</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-73.2912</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-3.77069</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-73.27883</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>365797</t>
+          <t>366264</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>601332</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.844742</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-73.386899</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>-3.77915</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-73.28175</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>366344</t>
+          <t>366259</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>601409</t>
+          <t>601331</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.79036</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-73.30287</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>-4.021036</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-73.432948</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>651138</t>
+          <t>366216</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FUENTE DE SABER / FUENTE DEL SABER</t>
+          <t>601325 CARMEN ROSA PANDURO RAMIREZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.76822</t>
+          <t>382</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-73.27496</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-3.76663</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-73.28214</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>365434</t>
+          <t>366202</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60102</t>
+          <t>601324 VIRGEN DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.889641</t>
+          <t>605</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-73.353906</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>-3.7733</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-73.28112</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>365599</t>
+          <t>365797</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60128 MARIA ANTONIETA RODRIGUEZ MACEDA</t>
+          <t>60778</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.863287</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-73.336562</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-3.844742</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-73.386899</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>366202</t>
+          <t>365622</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>601324 VIRGEN DE LAS MERCEDES</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.7733</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-73.28112</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>-4.231024</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-73.48778</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>815559</t>
+          <t>365599</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>601747</t>
+          <t>60128 MARIA ANTONIETA RODRIGUEZ MACEDA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.874315</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-73.358578</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>-3.863287</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-73.336562</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>-3.780437</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-73.312084</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>740795</t>
+          <t>365491</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>601608</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.84446</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-73.339311</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>-3.823057</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-73.326394</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>366363</t>
+          <t>365434</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>601411 MELVIN JONES</t>
+          <t>60102</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.761201</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-73.272904</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>-3.889641</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-73.353906</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>740936</t>
+          <t>365373</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>601606 VIOLETA CORREA DE BELAUNDE</t>
+          <t>60094</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.781896</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-73.273662</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>-3.828828</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-73.355177</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>366730</t>
+          <t>365368</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6010194 MARIA SOCORRO MENDOZA MENDOZA / 794</t>
+          <t>60093 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.783177</t>
+          <t>917</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-73.299151</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>-3.80519</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-73.340785</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>366810</t>
+          <t>365226</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6010275 FRANCISCO SECADA VIGNETTA</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.78161</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-73.29532</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>-3.786487</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-73.339115</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>367466</t>
+          <t>365194</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 46 WILHEM ROSSMAN</t>
+          <t>60024 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.77839</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-73.29181</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>-3.77449</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-73.29006</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>364849</t>
+          <t>364905</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>APLICACION UNAP</t>
+          <t>692</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.7815</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-73.28538</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>-3.78891</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-73.29935</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>366513</t>
+          <t>364887</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>601497</t>
+          <t>690 SANTA MONICA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.7853</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-73.2869</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>-3.76748</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-73.27315</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>365368</t>
+          <t>364849</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60093 JOSE OLAYA BALANDRA</t>
+          <t>APLICACION UNAP</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.80519</t>
+          <t>898</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-73.340785</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>-3.7815</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-73.28538</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>365226</t>
+          <t>364726</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>591</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.786487</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-73.339115</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>-3.78219</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-73.28514</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>364458</t>
+          <t>364670</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>474 ANGELITOS DEL SABER</t>
+          <t>548 MI MUNDO INFANTIL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.77282</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-73.28157</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>-3.7792</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-73.2912</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>367961</t>
+          <t>364552</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNAP MARIA REICHE</t>
+          <t>530</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.766469</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-73.273014</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>-3.843849</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-73.33998</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>365491</t>
+          <t>364458</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>474 ANGELITOS DEL SABER</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-3.823057</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-73.326394</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>-3.77282</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-73.28157</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>366768</t>
+          <t>364364</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6010227 CLUB DE LEONES DE LEMGO ALEMANIA</t>
+          <t>396 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-3.78157</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-73.28209</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>-3.766563</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-73.278856</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>366589</t>
+          <t>364321</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>601515</t>
+          <t>364</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-3.79122</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-73.29419</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>-3.76677</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-73.2793</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>367193</t>
+          <t>364302</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>601491 MADRE TERESA DE CALCUTA</t>
+          <t>348 DELIA PEREA TORRES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-3.79099</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-73.3012</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>-3.823355</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-73.327972</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>364552</t>
+          <t>364217</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>318 GLORIA CHAVEZ CULQUI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-3.843849</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-73.33998</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-3.77391</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-73.29031</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>364887</t>
+          <t>364203</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>690 SANTA MONICA</t>
+          <t>317</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-3.76748</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-73.27315</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-3.7739</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-73.27485</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>364905</t>
+          <t>364076</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>168 GOTITAS DEL SABER</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3.78891</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-73.29935</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-3.78597</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-73.339728</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>559578</t>
+          <t>364043</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>158 MI SEGUNDA CASITA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.795034</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-73.336111</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-3.7901</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-73.2935</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">

--- a/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/ZonasEscolares/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
